--- a/trade-elasticities-cointegration/outputs/14_reproducibility/section_14_reproducibility_check.xlsx
+++ b/trade-elasticities-cointegration/outputs/14_reproducibility/section_14_reproducibility_check.xlsx
@@ -982,7 +982,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2">
-        <v>46192.07774283063</v>
+        <v>46199.12570221657</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>

--- a/trade-elasticities-cointegration/outputs/14_reproducibility/section_14_reproducibility_check.xlsx
+++ b/trade-elasticities-cointegration/outputs/14_reproducibility/section_14_reproducibility_check.xlsx
@@ -927,7 +927,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -956,25 +956,35 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>processed_delivery_dir</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>processed_auxiliary_dir</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>figures_dir</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>all_final_checks_passed</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>n_missing_outputs</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>n_econometric_models</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>n_model_diagnostic_alerts</t>
         </is>
@@ -982,7 +992,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2">
-        <v>46199.12570221657</v>
+        <v>46210.58660876787</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -1001,19 +1011,29 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>C:/Users/julla/GitHub/applied-time-series-econometrics/trade-elasticities-cointegration/data/processed/final_data_panel</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>C:/Users/julla/GitHub/applied-time-series-econometrics/trade-elasticities-cointegration/data/processed/auxiliary_data</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
           <t>C:/Users/julla/GitHub/applied-time-series-econometrics/trade-elasticities-cointegration/figures</t>
         </is>
       </c>
-      <c r="F2" t="b">
-        <v>1</v>
-      </c>
-      <c r="G2">
+      <c r="H2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I2">
         <v>0</v>
       </c>
-      <c r="H2">
+      <c r="J2">
         <v>4</v>
       </c>
-      <c r="I2">
+      <c r="K2">
         <v>0</v>
       </c>
     </row>

--- a/trade-elasticities-cointegration/outputs/14_reproducibility/section_14_reproducibility_check.xlsx
+++ b/trade-elasticities-cointegration/outputs/14_reproducibility/section_14_reproducibility_check.xlsx
@@ -992,7 +992,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2">
-        <v>46210.58660876787</v>
+        <v>46211.00171353026</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>C:/Users/julla/GitHub/applied-time-series-econometrics/trade-elasticities-cointegration/data/processed/auxiliary_data</t>
+          <t>C:\Users\julla\AppData\Local\Temp\RtmpWqAhme/tp2_auxiliary_data</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
